--- a/Data/FlightPlan/FPL_21AUG26.xlsx
+++ b/Data/FlightPlan/FPL_21AUG26.xlsx
@@ -1178,6 +1178,9 @@
     <t>MEL</t>
   </si>
   <si>
+    <t>00:25</t>
+  </si>
+  <si>
     <t>VN-A815</t>
   </si>
   <si>
@@ -1214,7 +1217,7 @@
     <t>Total Record(s): 388</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 20, 2026 21:59</t>
+    <t xml:space="preserve">Generated on  Aug 21, 2026 01:44</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -15314,11 +15317,11 @@
         <v>252</v>
       </c>
       <c t="s" r="K456" s="7">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="L456" s="7"/>
       <c t="s" r="M456" s="7">
-        <v>371</v>
+        <v>389</v>
       </c>
     </row>
     <row r="457" ht="14.25" customHeight="1">
@@ -15350,9 +15353,13 @@
       <c t="s" r="J457" s="7">
         <v>18</v>
       </c>
-      <c r="K457" s="7"/>
+      <c t="s" r="K457" s="7">
+        <v>271</v>
+      </c>
       <c r="L457" s="7"/>
-      <c r="M457" s="7"/>
+      <c t="s" r="M457" s="7">
+        <v>369</v>
+      </c>
     </row>
     <row r="458" ht="14.25" customHeight="1">
       <c r="A458" s="6"/>
@@ -15381,7 +15388,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F459" s="7">
         <v>330</v>
@@ -15414,7 +15421,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F460" s="7">
         <v>330</v>
@@ -15423,7 +15430,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H460" s="8">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c t="s" r="I460" s="7">
         <v>228</v>
@@ -15447,13 +15454,13 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F461" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G461" s="8">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c t="s" r="H461" s="8">
         <v>27</v>
@@ -15495,7 +15502,7 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F463" s="7">
         <v>330</v>
@@ -15504,13 +15511,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H463" s="8">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c t="s" r="I463" s="7">
         <v>278</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
@@ -15528,13 +15535,13 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F464" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G464" s="8">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c t="s" r="H464" s="8">
         <v>37</v>
@@ -15543,7 +15550,7 @@
         <v>383</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
@@ -15576,7 +15583,7 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F466" s="7">
         <v>330</v>
@@ -15585,7 +15592,7 @@
         <v>37</v>
       </c>
       <c t="s" r="H466" s="8">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c t="s" r="I466" s="7">
         <v>288</v>
@@ -15609,13 +15616,13 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F467" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G467" s="8">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c t="s" r="H467" s="8">
         <v>37</v>
@@ -15657,7 +15664,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F469" s="7">
         <v>330</v>
@@ -15666,7 +15673,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H469" s="8">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c t="s" r="I469" s="7">
         <v>190</v>
@@ -15690,19 +15697,19 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F470" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G470" s="8">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c t="s" r="H470" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c t="s" r="J470" s="7">
         <v>345</v>
@@ -15713,7 +15720,7 @@
     </row>
     <row r="471" ht="15.75" customHeight="1">
       <c t="s" r="A471" s="9">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B471" s="9"/>
       <c r="C471" s="9"/>
@@ -15733,7 +15740,7 @@
     <row r="472" ht="65.25" customHeight="1"/>
     <row r="473" ht="16.5" customHeight="1">
       <c t="s" r="A473" s="10">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B473" s="10"/>
       <c r="C473" s="10"/>
@@ -15746,7 +15753,7 @@
       <c r="J473" s="10"/>
       <c r="K473" s="10"/>
       <c t="s" r="L473" s="11">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M473" s="11"/>
       <c r="N473" s="11"/>

--- a/Data/FlightPlan/FPL_21AUG26.xlsx
+++ b/Data/FlightPlan/FPL_21AUG26.xlsx
@@ -737,186 +737,186 @@
     <t>VN-A575</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>NOZ</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>DPS</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>TBB</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
     <t>11:30</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>NOZ</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>DPS</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>BLR</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>TBB</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
     <t>VN-A641</t>
   </si>
   <si>
@@ -1220,7 +1220,7 @@
     <t>Total Record(s): 388</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 21, 2026 03:21</t>
+    <t xml:space="preserve">Generated on  Aug 21, 2026 03:55</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -6892,11 +6892,11 @@
         <v>63</v>
       </c>
       <c t="s" r="K176" s="7">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>195</v>
+        <v>63</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -6907,7 +6907,7 @@
         <v>5068</v>
       </c>
       <c t="s" r="C177" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
@@ -6929,11 +6929,11 @@
         <v>129</v>
       </c>
       <c t="s" r="K177" s="7">
-        <v>223</v>
+        <v>65</v>
       </c>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>206</v>
+        <v>129</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -6944,7 +6944,7 @@
         <v>5068</v>
       </c>
       <c t="s" r="C178" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
@@ -6957,20 +6957,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c t="s" r="I178" s="7">
         <v>192</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c t="s" r="K178" s="7">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>200</v>
+        <v>244</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -6981,7 +6981,7 @@
         <v>5069</v>
       </c>
       <c t="s" r="C179" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
@@ -6991,16 +6991,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I179" s="7">
+        <v>245</v>
+      </c>
+      <c t="s" r="J179" s="7">
         <v>246</v>
-      </c>
-      <c t="s" r="J179" s="7">
-        <v>247</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7033,16 +7033,16 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
+        <v>247</v>
+      </c>
+      <c r="F181" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G181" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H181" s="8">
         <v>248</v>
-      </c>
-      <c r="F181" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G181" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H181" s="8">
-        <v>249</v>
       </c>
       <c t="s" r="I181" s="7">
         <v>211</v>
@@ -7066,13 +7066,13 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
+        <v>247</v>
+      </c>
+      <c r="F182" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G182" s="8">
         <v>248</v>
-      </c>
-      <c r="F182" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G182" s="8">
-        <v>249</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>16</v>
@@ -7081,7 +7081,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7108,13 +7108,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H183" s="8">
+        <v>250</v>
+      </c>
+      <c t="s" r="I183" s="7">
         <v>251</v>
       </c>
-      <c t="s" r="I183" s="7">
+      <c t="s" r="J183" s="7">
         <v>252</v>
-      </c>
-      <c t="s" r="J183" s="7">
-        <v>253</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7132,13 +7132,13 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>16</v>
@@ -7176,26 +7176,26 @@
         <v>7615</v>
       </c>
       <c t="s" r="C186" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
+        <v>253</v>
+      </c>
+      <c r="F186" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G186" s="8">
         <v>254</v>
       </c>
-      <c r="F186" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G186" s="8">
+      <c t="s" r="H186" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I186" s="7">
         <v>255</v>
       </c>
-      <c t="s" r="H186" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I186" s="7">
+      <c t="s" r="J186" s="7">
         <v>256</v>
-      </c>
-      <c t="s" r="J186" s="7">
-        <v>257</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7209,11 +7209,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C187" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7242,11 +7242,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C188" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7258,7 +7258,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c t="s" r="J188" s="7">
         <v>181</v>
@@ -7275,11 +7275,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C189" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7288,10 +7288,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H189" s="8">
+        <v>258</v>
+      </c>
+      <c t="s" r="I189" s="7">
         <v>259</v>
-      </c>
-      <c t="s" r="I189" s="7">
-        <v>260</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>49</v>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7360,7 +7360,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7393,16 +7393,16 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
+        <v>260</v>
+      </c>
+      <c r="F193" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G193" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H193" s="8">
         <v>261</v>
-      </c>
-      <c r="F193" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G193" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H193" s="8">
-        <v>262</v>
       </c>
       <c t="s" r="I193" s="7">
         <v>150</v>
@@ -7426,22 +7426,22 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
+        <v>260</v>
+      </c>
+      <c r="F194" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G194" s="8">
         <v>261</v>
       </c>
-      <c r="F194" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G194" s="8">
+      <c t="s" r="H194" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I194" s="7">
         <v>262</v>
       </c>
-      <c t="s" r="H194" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I194" s="7">
+      <c t="s" r="J194" s="7">
         <v>263</v>
-      </c>
-      <c t="s" r="J194" s="7">
-        <v>264</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7555,7 +7555,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7669,7 +7669,7 @@
         <v>136</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7720,7 +7720,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7729,13 +7729,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H204" s="8">
+        <v>268</v>
+      </c>
+      <c t="s" r="I204" s="7">
         <v>269</v>
       </c>
-      <c t="s" r="I204" s="7">
+      <c t="s" r="J204" s="7">
         <v>270</v>
-      </c>
-      <c t="s" r="J204" s="7">
-        <v>271</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7753,22 +7753,22 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I205" s="7">
+        <v>271</v>
+      </c>
+      <c t="s" r="J205" s="7">
         <v>272</v>
-      </c>
-      <c t="s" r="J205" s="7">
-        <v>273</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7801,22 +7801,22 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
+        <v>273</v>
+      </c>
+      <c r="F207" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G207" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H207" s="8">
         <v>274</v>
-      </c>
-      <c r="F207" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G207" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H207" s="8">
-        <v>275</v>
       </c>
       <c t="s" r="I207" s="7">
         <v>133</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7834,19 +7834,19 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
+        <v>273</v>
+      </c>
+      <c r="F208" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G208" s="8">
         <v>274</v>
       </c>
-      <c r="F208" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G208" s="8">
-        <v>275</v>
-      </c>
       <c t="s" r="H208" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>72</v>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7879,7 +7879,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>158</v>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7915,7 +7915,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7948,7 +7948,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7981,7 +7981,7 @@
         <v>217</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8026,7 +8026,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>147</v>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8089,7 +8089,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c t="s" r="I216" s="7">
         <v>108</v>
@@ -8113,22 +8113,22 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
+        <v>281</v>
+      </c>
+      <c t="s" r="H217" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I217" s="7">
         <v>282</v>
       </c>
-      <c t="s" r="H217" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I217" s="7">
+      <c t="s" r="J217" s="7">
         <v>283</v>
-      </c>
-      <c t="s" r="J217" s="7">
-        <v>284</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8155,10 +8155,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H218" s="8">
+        <v>284</v>
+      </c>
+      <c t="s" r="I218" s="7">
         <v>285</v>
-      </c>
-      <c t="s" r="I218" s="7">
-        <v>286</v>
       </c>
       <c t="s" r="J218" s="7">
         <v>111</v>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8209,7 +8209,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8227,7 +8227,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8242,7 +8242,7 @@
         <v>157</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8272,7 +8272,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c t="s" r="J222" s="7">
         <v>188</v>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8323,7 +8323,7 @@
         <v>229</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8350,13 +8350,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c t="s" r="I225" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8374,13 +8374,13 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>39</v>
@@ -8389,7 +8389,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8470,7 +8470,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8500,7 +8500,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>197</v>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8536,7 +8536,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8620,7 +8620,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8749,7 +8749,7 @@
         <v>228</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8800,7 +8800,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8845,10 +8845,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>242</v>
+        <v>301</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8911,10 +8911,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8959,7 +8959,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c t="s" r="J245" s="7">
         <v>137</v>
@@ -8992,10 +8992,10 @@
         <v>88</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>242</v>
+        <v>301</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9028,7 +9028,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9055,7 +9055,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c t="s" r="I248" s="7">
         <v>303</v>
@@ -9085,7 +9085,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>17</v>
@@ -9127,7 +9127,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9340,7 +9340,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9418,7 +9418,7 @@
         <v>99</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>87</v>
@@ -9565,10 +9565,10 @@
         <v>104</v>
       </c>
       <c t="s" r="I265" s="7">
+        <v>300</v>
+      </c>
+      <c t="s" r="J265" s="7">
         <v>301</v>
-      </c>
-      <c t="s" r="J265" s="7">
-        <v>242</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9763,7 +9763,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>124</v>
@@ -9880,7 +9880,7 @@
         <v>314</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9910,7 +9910,7 @@
         <v>88</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>233</v>
@@ -9991,7 +9991,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>20</v>
@@ -10300,7 +10300,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c t="s" r="I289" s="7">
         <v>320</v>
@@ -10330,7 +10330,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>17</v>
@@ -10387,7 +10387,7 @@
         <v>317</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10420,7 +10420,7 @@
         <v>165</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10978,7 +10978,7 @@
         <v>170</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11059,7 +11059,7 @@
         <v>190</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11092,7 +11092,7 @@
         <v>127</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11155,7 +11155,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>67</v>
@@ -11383,10 +11383,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11419,7 +11419,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11452,7 +11452,7 @@
         <v>337</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11494,7 +11494,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c t="s" r="I329" s="7">
         <v>124</v>
@@ -11524,7 +11524,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c t="s" r="H330" s="8">
         <v>17</v>
@@ -11746,7 +11746,7 @@
         <v>335</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>242</v>
+        <v>301</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11812,7 +11812,7 @@
         <v>311</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11842,7 +11842,7 @@
         <v>344</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>34</v>
@@ -11875,7 +11875,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>345</v>
@@ -12172,7 +12172,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12286,7 +12286,7 @@
         <v>235</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12349,7 +12349,7 @@
         <v>99</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>206</v>
@@ -12490,7 +12490,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>17</v>
@@ -12907,7 +12907,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>209</v>
@@ -12958,7 +12958,7 @@
         <v>357</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12988,7 +12988,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>242</v>
+        <v>301</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>78</v>
@@ -13099,7 +13099,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c t="s" r="I382" s="7">
         <v>319</v>
@@ -13129,7 +13129,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>27</v>
@@ -13165,13 +13165,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c t="s" r="I384" s="7">
         <v>170</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13195,7 +13195,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>27</v>
@@ -13318,7 +13318,7 @@
         <v>163</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13396,7 +13396,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c t="s" r="J392" s="7">
         <v>49</v>
@@ -13741,7 +13741,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>198</v>
@@ -14056,7 +14056,7 @@
         <v>372</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14101,7 +14101,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>324</v>
@@ -14203,7 +14203,7 @@
         <v>193</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14311,7 +14311,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c t="s" r="I422" s="7">
         <v>206</v>
@@ -14341,7 +14341,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>16</v>
@@ -14413,7 +14413,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c t="s" r="J425" s="7">
         <v>377</v>
@@ -14593,10 +14593,10 @@
         <v>167</v>
       </c>
       <c t="s" r="I431" s="7">
+        <v>282</v>
+      </c>
+      <c t="s" r="J431" s="7">
         <v>283</v>
-      </c>
-      <c t="s" r="J431" s="7">
-        <v>284</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14674,7 +14674,7 @@
         <v>205</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c t="s" r="J434" s="7">
         <v>78</v>
@@ -14743,7 +14743,7 @@
         <v>380</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -14821,7 +14821,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c t="s" r="J439" s="7">
         <v>53</v>
@@ -14887,7 +14887,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c t="s" r="J441" s="7">
         <v>160</v>
@@ -14956,7 +14956,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -15034,7 +15034,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c t="s" r="J446" s="7">
         <v>97</v>
@@ -15070,7 +15070,7 @@
         <v>168</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -15331,7 +15331,7 @@
         <v>97</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c t="s" r="K456" s="7">
         <v>78</v>
@@ -15371,7 +15371,7 @@
         <v>18</v>
       </c>
       <c t="s" r="K457" s="7">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L457" s="7"/>
       <c t="s" r="M457" s="7">
@@ -15417,10 +15417,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
@@ -15531,7 +15531,7 @@
         <v>394</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c t="s" r="J463" s="7">
         <v>395</v>
@@ -15596,7 +15596,7 @@
         <v>5805</v>
       </c>
       <c t="s" r="C466" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
@@ -15612,7 +15612,7 @@
         <v>398</v>
       </c>
       <c t="s" r="I466" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c t="s" r="J466" s="7">
         <v>203</v>
@@ -15629,7 +15629,7 @@
         <v>5806</v>
       </c>
       <c t="s" r="C467" s="7">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">

--- a/Data/FlightPlan/FPL_21AUG26.xlsx
+++ b/Data/FlightPlan/FPL_21AUG26.xlsx
@@ -266,6 +266,36 @@
     <t>VN-A521</t>
   </si>
   <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A522</t>
+  </si>
+  <si>
     <t>05:40</t>
   </si>
   <si>
@@ -290,36 +320,6 @@
     <t>RMQ</t>
   </si>
   <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>VN-A522</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
     <t>VN-A523</t>
   </si>
   <si>
@@ -584,6 +584,9 @@
     <t>09:40</t>
   </si>
   <si>
+    <t>10:07</t>
+  </si>
+  <si>
     <t>13:10</t>
   </si>
   <si>
@@ -1052,6 +1055,9 @@
     <t>VN-A667</t>
   </si>
   <si>
+    <t>06:33</t>
+  </si>
+  <si>
     <t>07:20</t>
   </si>
   <si>
@@ -1157,6 +1163,9 @@
     <t>VN-A698</t>
   </si>
   <si>
+    <t>06:57</t>
+  </si>
+  <si>
     <t>VN-A699</t>
   </si>
   <si>
@@ -1220,7 +1229,7 @@
     <t>Total Record(s): 388</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 21, 2026 03:55</t>
+    <t xml:space="preserve">Generated on  Aug 21, 2026 05:09</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2755,7 +2764,7 @@
         <v>13</v>
       </c>
       <c r="B40" s="7">
-        <v>501</v>
+        <v>901</v>
       </c>
       <c t="s" r="C40" s="7">
         <v>14</v>
@@ -2771,13 +2780,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H40" s="8">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c t="s" r="I40" s="7">
         <v>85</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -2788,7 +2797,7 @@
         <v>13</v>
       </c>
       <c r="B41" s="7">
-        <v>514</v>
+        <v>902</v>
       </c>
       <c t="s" r="C41" s="7">
         <v>14</v>
@@ -2801,7 +2810,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G41" s="8">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c t="s" r="H41" s="8">
         <v>17</v>
@@ -2810,7 +2819,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -2821,7 +2830,7 @@
         <v>13</v>
       </c>
       <c r="B42" s="7">
-        <v>563</v>
+        <v>465</v>
       </c>
       <c t="s" r="C42" s="7">
         <v>14</v>
@@ -2837,10 +2846,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H42" s="8">
+        <v>87</v>
+      </c>
+      <c t="s" r="I42" s="7">
         <v>88</v>
-      </c>
-      <c t="s" r="I42" s="7">
-        <v>72</v>
       </c>
       <c t="s" r="J42" s="7">
         <v>89</v>
@@ -2854,7 +2863,7 @@
         <v>13</v>
       </c>
       <c r="B43" s="7">
-        <v>564</v>
+        <v>466</v>
       </c>
       <c t="s" r="C43" s="7">
         <v>14</v>
@@ -2867,7 +2876,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G43" s="8">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c t="s" r="H43" s="8">
         <v>17</v>
@@ -2884,10 +2893,10 @@
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c t="s" r="A44" s="6">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B44" s="7">
-        <v>948</v>
+        <v>920</v>
       </c>
       <c t="s" r="C44" s="7">
         <v>14</v>
@@ -2906,61 +2915,43 @@
         <v>92</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
       <c r="M44" s="7"/>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c t="s" r="A45" s="6">
-        <v>13</v>
-      </c>
-      <c r="B45" s="7">
-        <v>949</v>
-      </c>
-      <c t="s" r="C45" s="7">
-        <v>14</v>
-      </c>
+      <c r="A45" s="6"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
       <c r="D45" s="7"/>
-      <c t="s" r="E45" s="7">
-        <v>84</v>
-      </c>
-      <c r="F45" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G45" s="8">
-        <v>92</v>
-      </c>
-      <c t="s" r="H45" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I45" s="7">
-        <v>57</v>
-      </c>
-      <c t="s" r="J45" s="7">
-        <v>29</v>
-      </c>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
       <c r="M45" s="7"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c t="s" r="A46" s="6">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B46" s="7">
-        <v>920</v>
+        <v>501</v>
       </c>
       <c t="s" r="C46" s="7">
         <v>14</v>
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -2969,29 +2960,47 @@
         <v>17</v>
       </c>
       <c t="s" r="H46" s="8">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c t="s" r="I46" s="7">
         <v>95</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="6"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
+      <c t="s" r="A47" s="6">
+        <v>13</v>
+      </c>
+      <c r="B47" s="7">
+        <v>514</v>
+      </c>
+      <c t="s" r="C47" s="7">
+        <v>14</v>
+      </c>
       <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
+      <c t="s" r="E47" s="7">
+        <v>94</v>
+      </c>
+      <c r="F47" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G47" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H47" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I47" s="7">
+        <v>96</v>
+      </c>
+      <c t="s" r="J47" s="7">
+        <v>97</v>
+      </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
@@ -3001,14 +3010,14 @@
         <v>13</v>
       </c>
       <c r="B48" s="7">
-        <v>901</v>
+        <v>563</v>
       </c>
       <c t="s" r="C48" s="7">
         <v>14</v>
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -3017,13 +3026,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H48" s="8">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
@@ -3034,29 +3043,29 @@
         <v>13</v>
       </c>
       <c r="B49" s="7">
-        <v>902</v>
+        <v>564</v>
       </c>
       <c t="s" r="C49" s="7">
         <v>14</v>
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G49" s="8">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c t="s" r="H49" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3067,14 +3076,14 @@
         <v>13</v>
       </c>
       <c r="B50" s="7">
-        <v>465</v>
+        <v>948</v>
       </c>
       <c t="s" r="C50" s="7">
         <v>14</v>
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3083,13 +3092,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H50" s="8">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3100,29 +3109,29 @@
         <v>13</v>
       </c>
       <c r="B51" s="7">
-        <v>466</v>
+        <v>949</v>
       </c>
       <c t="s" r="C51" s="7">
         <v>14</v>
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G51" s="8">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c t="s" r="H51" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3341,7 +3350,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G59" s="8">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c t="s" r="H59" s="8">
         <v>17</v>
@@ -3560,7 +3569,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c t="s" r="J66" s="7">
         <v>81</v>
@@ -3773,7 +3782,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c t="s" r="J73" s="7">
         <v>81</v>
@@ -3923,7 +3932,7 @@
         <v>144</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -3988,7 +3997,7 @@
         <v>148</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c t="s" r="J80" s="7">
         <v>149</v>
@@ -4054,7 +4063,7 @@
         <v>151</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c t="s" r="J82" s="7">
         <v>152</v>
@@ -4198,7 +4207,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H87" s="8">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c t="s" r="I87" s="7">
         <v>40</v>
@@ -4228,13 +4237,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G88" s="8">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c t="s" r="H88" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c t="s" r="J88" s="7">
         <v>159</v>
@@ -4843,7 +4852,7 @@
         <v>113</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -5093,7 +5102,9 @@
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
-      <c r="M116" s="7"/>
+      <c t="s" r="M116" s="7">
+        <v>191</v>
+      </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
       <c t="s" r="A117" s="6">
@@ -5119,10 +5130,10 @@
         <v>148</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5152,7 +5163,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>58</v>
@@ -5188,7 +5199,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5221,7 +5232,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5230,13 +5241,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c t="s" r="I121" s="7">
         <v>190</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5254,13 +5265,13 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>27</v>
@@ -5287,7 +5298,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5299,7 +5310,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J123" s="7">
         <v>44</v>
@@ -5320,7 +5331,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5353,7 +5364,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5401,7 +5412,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5410,13 +5421,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c t="s" r="I127" s="7">
         <v>20</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5434,19 +5445,19 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G128" s="8">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c t="s" r="H128" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c t="s" r="J128" s="7">
         <v>54</v>
@@ -5467,7 +5478,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5482,7 +5493,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5500,7 +5511,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5533,7 +5544,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5545,7 +5556,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J131" s="7">
         <v>75</v>
@@ -5566,7 +5577,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5578,10 +5589,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5614,7 +5625,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5629,7 +5640,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5647,7 +5658,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5680,7 +5691,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5728,7 +5739,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5737,13 +5748,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="I138" s="7">
         <v>147</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5761,13 +5772,13 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>16</v>
@@ -5776,7 +5787,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5794,7 +5805,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5809,7 +5820,7 @@
         <v>119</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5827,7 +5838,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5839,10 +5850,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5860,7 +5871,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5875,7 +5886,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5908,7 +5919,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5920,7 +5931,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>137</v>
@@ -5941,7 +5952,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5953,7 +5964,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>56</v>
@@ -5974,7 +5985,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -5986,10 +5997,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6007,7 +6018,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6019,10 +6030,10 @@
         <v>79</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6040,7 +6051,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6052,7 +6063,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J148" s="7">
         <v>163</v>
@@ -6073,7 +6084,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6085,7 +6096,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>188</v>
@@ -6121,7 +6132,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6133,7 +6144,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J151" s="7">
         <v>56</v>
@@ -6154,7 +6165,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6166,7 +6177,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J152" s="7">
         <v>129</v>
@@ -6187,7 +6198,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6199,7 +6210,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J153" s="7">
         <v>58</v>
@@ -6220,7 +6231,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6232,7 +6243,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>146</v>
@@ -6268,7 +6279,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6280,10 +6291,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6301,7 +6312,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6316,7 +6327,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6334,7 +6345,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6346,7 +6357,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J158" s="7">
         <v>59</v>
@@ -6367,7 +6378,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6379,7 +6390,7 @@
         <v>61</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>190</v>
@@ -6415,26 +6426,28 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
-      <c r="M161" s="7"/>
+      <c t="s" r="M161" s="7">
+        <v>97</v>
+      </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
       <c t="s" r="A162" s="6">
@@ -6448,7 +6461,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6481,7 +6494,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6490,10 +6503,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>80</v>
@@ -6514,22 +6527,22 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>51</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6547,7 +6560,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6556,13 +6569,13 @@
         <v>51</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c t="s" r="I165" s="7">
         <v>119</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6580,13 +6593,13 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>27</v>
@@ -6613,7 +6626,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6625,10 +6638,10 @@
         <v>61</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6661,7 +6674,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6673,10 +6686,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6694,7 +6707,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6709,7 +6722,7 @@
         <v>183</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6727,7 +6740,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6760,7 +6773,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6772,7 +6785,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>57</v>
@@ -6793,7 +6806,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6802,13 +6815,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="I173" s="7">
         <v>163</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6826,22 +6839,22 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6874,7 +6887,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6907,11 +6920,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C177" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6944,11 +6957,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C178" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6957,20 +6970,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="K178" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -6981,26 +6994,26 @@
         <v>5069</v>
       </c>
       <c t="s" r="C179" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7033,7 +7046,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7042,10 +7055,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>63</v>
@@ -7066,13 +7079,13 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>16</v>
@@ -7081,7 +7094,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7099,7 +7112,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7108,13 +7121,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7132,13 +7145,13 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>16</v>
@@ -7147,7 +7160,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7176,26 +7189,26 @@
         <v>7615</v>
       </c>
       <c t="s" r="C186" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7209,11 +7222,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C187" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7242,11 +7255,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C188" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7258,7 +7271,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J188" s="7">
         <v>181</v>
@@ -7275,11 +7288,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C189" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7288,10 +7301,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>49</v>
@@ -7327,7 +7340,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7342,7 +7355,7 @@
         <v>156</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7360,7 +7373,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7393,7 +7406,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7402,13 +7415,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="I193" s="7">
         <v>150</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7426,22 +7439,22 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7474,7 +7487,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7489,7 +7502,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7507,7 +7520,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7519,10 +7532,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7540,7 +7553,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7555,7 +7568,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7588,7 +7601,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7621,7 +7634,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7636,7 +7649,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7654,7 +7667,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7663,13 +7676,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c t="s" r="I202" s="7">
         <v>136</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7687,19 +7700,19 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>57</v>
@@ -7720,7 +7733,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7729,13 +7742,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7753,22 +7766,22 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7801,7 +7814,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7810,13 +7823,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="I207" s="7">
         <v>133</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7834,19 +7847,19 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>72</v>
@@ -7867,7 +7880,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7879,7 +7892,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>158</v>
@@ -7900,7 +7913,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7915,7 +7928,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7933,7 +7946,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7948,7 +7961,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7966,7 +7979,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7978,10 +7991,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8014,7 +8027,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8026,14 +8039,16 @@
         <v>37</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>147</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
-      <c r="M214" s="7"/>
+      <c t="s" r="M214" s="7">
+        <v>191</v>
+      </c>
     </row>
     <row r="215" ht="15" customHeight="1">
       <c t="s" r="A215" s="6">
@@ -8047,7 +8062,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8080,7 +8095,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8089,13 +8104,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="I216" s="7">
         <v>108</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8113,22 +8128,22 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8146,7 +8161,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8155,10 +8170,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J218" s="7">
         <v>111</v>
@@ -8194,7 +8209,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8209,7 +8224,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8227,7 +8242,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8242,7 +8257,7 @@
         <v>157</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8260,7 +8275,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8272,7 +8287,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="J222" s="7">
         <v>188</v>
@@ -8308,7 +8323,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8320,10 +8335,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8341,7 +8356,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8350,13 +8365,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="I225" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8374,13 +8389,13 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>39</v>
@@ -8389,7 +8404,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8407,7 +8422,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8455,7 +8470,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8470,7 +8485,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8488,7 +8503,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8500,10 +8515,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8521,7 +8536,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8533,10 +8548,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8554,7 +8569,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8569,7 +8584,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8587,7 +8602,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8596,7 +8611,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c t="s" r="I233" s="7">
         <v>129</v>
@@ -8620,13 +8635,13 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>16</v>
@@ -8635,7 +8650,7 @@
         <v>170</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8653,7 +8668,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8686,7 +8701,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8734,7 +8749,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8746,10 +8761,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8767,7 +8782,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8782,7 +8797,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8800,7 +8815,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8833,7 +8848,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8845,10 +8860,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8866,7 +8881,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8899,7 +8914,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8911,10 +8926,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8947,7 +8962,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -8959,7 +8974,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J245" s="7">
         <v>137</v>
@@ -8980,22 +8995,22 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
+        <v>303</v>
+      </c>
+      <c r="F246" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G246" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H246" s="8">
+        <v>98</v>
+      </c>
+      <c t="s" r="I246" s="7">
         <v>302</v>
       </c>
-      <c r="F246" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G246" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H246" s="8">
-        <v>88</v>
-      </c>
-      <c t="s" r="I246" s="7">
-        <v>301</v>
-      </c>
       <c t="s" r="J246" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9013,13 +9028,13 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>17</v>
@@ -9028,7 +9043,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9046,7 +9061,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9055,13 +9070,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9079,22 +9094,22 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9112,7 +9127,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9127,7 +9142,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9145,7 +9160,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9160,7 +9175,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9193,7 +9208,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9226,7 +9241,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9238,7 +9253,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J254" s="7">
         <v>127</v>
@@ -9259,7 +9274,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9292,7 +9307,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9304,10 +9319,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9325,7 +9340,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9340,7 +9355,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9358,7 +9373,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9370,10 +9385,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9406,7 +9421,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9415,13 +9430,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9439,13 +9454,13 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>17</v>
@@ -9454,7 +9469,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9472,7 +9487,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9487,7 +9502,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9505,7 +9520,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9517,7 +9532,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>82</v>
@@ -9553,7 +9568,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9565,10 +9580,10 @@
         <v>104</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9586,7 +9601,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9598,10 +9613,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9619,7 +9634,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9628,13 +9643,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c t="s" r="I267" s="7">
         <v>44</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9652,13 +9667,13 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>17</v>
@@ -9667,7 +9682,7 @@
         <v>119</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9685,7 +9700,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9697,10 +9712,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9718,7 +9733,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9751,7 +9766,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9763,7 +9778,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>124</v>
@@ -9799,7 +9814,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9811,7 +9826,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>42</v>
@@ -9832,7 +9847,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9865,7 +9880,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9877,10 +9892,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9898,7 +9913,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -9907,13 +9922,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9931,13 +9946,13 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>16</v>
@@ -9979,7 +9994,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -9991,7 +10006,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>20</v>
@@ -10012,7 +10027,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10027,7 +10042,7 @@
         <v>113</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10045,7 +10060,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10057,7 +10072,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>169</v>
@@ -10078,7 +10093,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10090,10 +10105,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10111,7 +10126,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10144,7 +10159,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10159,7 +10174,7 @@
         <v>141</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10192,7 +10207,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10207,7 +10222,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10225,7 +10240,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10237,7 +10252,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>106</v>
@@ -10258,7 +10273,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10270,10 +10285,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10291,7 +10306,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10300,10 +10315,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>83</v>
@@ -10324,13 +10339,13 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>17</v>
@@ -10339,7 +10354,7 @@
         <v>173</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10372,7 +10387,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -10384,10 +10399,10 @@
         <v>115</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10405,7 +10420,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10420,7 +10435,7 @@
         <v>165</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10438,7 +10453,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10447,13 +10462,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="I294" s="7">
         <v>126</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10471,22 +10486,22 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10504,7 +10519,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10516,10 +10531,10 @@
         <v>128</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10537,7 +10552,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10552,7 +10567,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10570,7 +10585,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10582,10 +10597,10 @@
         <v>167</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10603,7 +10618,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10618,7 +10633,7 @@
         <v>140</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10651,7 +10666,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10666,7 +10681,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10684,7 +10699,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -10717,7 +10732,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -10729,7 +10744,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>114</v>
@@ -10750,7 +10765,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -10783,7 +10798,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -10795,10 +10810,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10816,7 +10831,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -10825,13 +10840,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10864,7 +10879,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -10873,7 +10888,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="I308" s="7">
         <v>42</v>
@@ -10897,13 +10912,13 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>16</v>
@@ -10912,7 +10927,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10930,7 +10945,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -10942,7 +10957,7 @@
         <v>115</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>82</v>
@@ -10963,7 +10978,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -10978,7 +10993,7 @@
         <v>170</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11011,7 +11026,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11044,7 +11059,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11059,7 +11074,7 @@
         <v>190</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11077,7 +11092,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11092,7 +11107,7 @@
         <v>127</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11110,7 +11125,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11119,13 +11134,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11143,19 +11158,19 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>67</v>
@@ -11191,7 +11206,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11203,7 +11218,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="J319" s="7">
         <v>185</v>
@@ -11224,7 +11239,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11236,7 +11251,7 @@
         <v>61</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>111</v>
@@ -11272,7 +11287,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11284,10 +11299,10 @@
         <v>167</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11305,7 +11320,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11338,7 +11353,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11350,10 +11365,10 @@
         <v>167</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11371,7 +11386,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11383,10 +11398,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11404,7 +11419,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11413,13 +11428,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="I326" s="7">
         <v>129</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11437,22 +11452,22 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="H327" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11485,7 +11500,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11494,13 +11509,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="I329" s="7">
         <v>124</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11518,19 +11533,19 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="H330" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>137</v>
@@ -11551,7 +11566,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11584,7 +11599,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11599,7 +11614,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11617,7 +11632,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11629,10 +11644,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11650,7 +11665,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11665,7 +11680,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11698,7 +11713,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -11731,7 +11746,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11743,10 +11758,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11764,7 +11779,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -11779,7 +11794,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11797,7 +11812,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -11809,10 +11824,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11830,7 +11845,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -11839,10 +11854,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>34</v>
@@ -11863,22 +11878,22 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11911,7 +11926,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -11923,14 +11938,16 @@
         <v>51</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>178</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
-      <c r="M343" s="7"/>
+      <c t="s" r="M343" s="7">
+        <v>348</v>
+      </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
       <c t="s" r="A344" s="6">
@@ -11944,7 +11961,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -11956,10 +11973,10 @@
         <v>167</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11977,7 +11994,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -11989,10 +12006,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12010,7 +12027,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12022,7 +12039,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>78</v>
@@ -12043,7 +12060,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12055,10 +12072,10 @@
         <v>177</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12076,7 +12093,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12124,7 +12141,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12139,7 +12156,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12157,7 +12174,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12172,7 +12189,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12190,7 +12207,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12202,7 +12219,7 @@
         <v>115</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>26</v>
@@ -12223,7 +12240,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12271,7 +12288,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12283,10 +12300,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12304,7 +12321,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12337,7 +12354,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12346,13 +12363,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12370,13 +12387,13 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>17</v>
@@ -12403,7 +12420,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
@@ -12412,13 +12429,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="I359" s="7">
         <v>180</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12436,22 +12453,22 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12484,22 +12501,22 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12517,7 +12534,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12550,7 +12567,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12562,7 +12579,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J364" s="7">
         <v>117</v>
@@ -12583,7 +12600,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12616,7 +12633,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12628,10 +12645,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12649,7 +12666,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12661,7 +12678,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>153</v>
@@ -12697,7 +12714,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -12712,7 +12729,7 @@
         <v>154</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12730,7 +12747,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -12745,7 +12762,7 @@
         <v>135</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12763,7 +12780,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -12796,7 +12813,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -12808,7 +12825,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J372" s="7">
         <v>44</v>
@@ -12829,7 +12846,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -12841,10 +12858,10 @@
         <v>79</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12862,7 +12879,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -12874,10 +12891,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12895,7 +12912,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -12907,10 +12924,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12943,7 +12960,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -12955,10 +12972,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12976,7 +12993,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -12988,7 +13005,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>78</v>
@@ -13009,7 +13026,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -13057,7 +13074,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13069,7 +13086,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>136</v>
@@ -13090,7 +13107,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13099,10 +13116,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J382" s="7">
         <v>80</v>
@@ -13123,13 +13140,13 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>27</v>
@@ -13138,7 +13155,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13156,7 +13173,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13165,13 +13182,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="I384" s="7">
         <v>170</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13189,19 +13206,19 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>188</v>
@@ -13237,7 +13254,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13270,7 +13287,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
@@ -13279,7 +13296,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c t="s" r="I388" s="7">
         <v>65</v>
@@ -13303,13 +13320,13 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c t="s" r="H389" s="8">
         <v>16</v>
@@ -13318,7 +13335,7 @@
         <v>163</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13351,7 +13368,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -13366,7 +13383,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13384,7 +13401,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -13396,7 +13413,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="J392" s="7">
         <v>49</v>
@@ -13417,7 +13434,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -13426,13 +13443,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c t="s" r="I393" s="7">
         <v>53</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13450,13 +13467,13 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>17</v>
@@ -13483,7 +13500,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -13495,10 +13512,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13516,7 +13533,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -13531,7 +13548,7 @@
         <v>185</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13549,7 +13566,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -13561,10 +13578,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13582,7 +13599,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -13630,7 +13647,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -13639,7 +13656,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c t="s" r="I400" s="7">
         <v>69</v>
@@ -13663,13 +13680,13 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>16</v>
@@ -13678,7 +13695,7 @@
         <v>156</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13696,7 +13713,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -13708,7 +13725,7 @@
         <v>104</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>56</v>
@@ -13729,7 +13746,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -13741,10 +13758,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13762,7 +13779,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -13771,10 +13788,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>185</v>
@@ -13795,22 +13812,22 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c t="s" r="H405" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13843,7 +13860,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -13855,10 +13872,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13876,7 +13893,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -13888,7 +13905,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>53</v>
@@ -13909,7 +13926,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -13942,7 +13959,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -13957,7 +13974,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -13975,7 +13992,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -13990,7 +14007,7 @@
         <v>161</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14008,7 +14025,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14023,7 +14040,7 @@
         <v>185</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14041,7 +14058,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -14053,10 +14070,10 @@
         <v>61</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14089,7 +14106,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -14101,10 +14118,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14122,7 +14139,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14134,10 +14151,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14155,7 +14172,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14167,10 +14184,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14188,7 +14205,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14200,10 +14217,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14236,7 +14253,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -14245,7 +14262,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c t="s" r="I420" s="7">
         <v>20</v>
@@ -14269,13 +14286,13 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G421" s="8">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c t="s" r="H421" s="8">
         <v>16</v>
@@ -14302,7 +14319,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -14311,10 +14328,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>66</v>
@@ -14335,22 +14352,22 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14368,7 +14385,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -14380,7 +14397,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>31</v>
@@ -14401,7 +14418,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -14413,10 +14430,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14449,7 +14466,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
@@ -14482,7 +14499,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
@@ -14515,7 +14532,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F429" s="7">
         <v>320</v>
@@ -14527,10 +14544,10 @@
         <v>128</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -14548,7 +14565,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F430" s="7">
         <v>320</v>
@@ -14563,7 +14580,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14581,7 +14598,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F431" s="7">
         <v>320</v>
@@ -14593,10 +14610,10 @@
         <v>167</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14614,7 +14631,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F432" s="7">
         <v>320</v>
@@ -14626,7 +14643,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="J432" s="7">
         <v>109</v>
@@ -14662,7 +14679,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -14671,10 +14688,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J434" s="7">
         <v>78</v>
@@ -14695,19 +14712,19 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="H435" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c t="s" r="J435" s="7">
         <v>170</v>
@@ -14728,7 +14745,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
@@ -14740,10 +14757,10 @@
         <v>77</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -14776,7 +14793,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
@@ -14788,14 +14805,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c t="s" r="J438" s="7">
         <v>124</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
-      <c r="M438" s="7"/>
+      <c t="s" r="M438" s="7">
+        <v>384</v>
+      </c>
     </row>
     <row r="439" ht="14.25" customHeight="1">
       <c t="s" r="A439" s="6">
@@ -14809,7 +14828,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -14821,7 +14840,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="J439" s="7">
         <v>53</v>
@@ -14842,7 +14861,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
@@ -14854,7 +14873,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J440" s="7">
         <v>23</v>
@@ -14875,7 +14894,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -14887,7 +14906,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J441" s="7">
         <v>160</v>
@@ -14908,7 +14927,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F442" s="7">
         <v>321</v>
@@ -14923,7 +14942,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -14941,7 +14960,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
@@ -14956,7 +14975,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -14989,7 +15008,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F445" s="7">
         <v>320</v>
@@ -15001,7 +15020,7 @@
         <v>115</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="J445" s="7">
         <v>147</v>
@@ -15022,7 +15041,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F446" s="7">
         <v>320</v>
@@ -15034,10 +15053,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
@@ -15055,7 +15074,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F447" s="7">
         <v>320</v>
@@ -15070,7 +15089,7 @@
         <v>168</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -15088,7 +15107,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F448" s="7">
         <v>320</v>
@@ -15103,7 +15122,7 @@
         <v>149</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -15121,7 +15140,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F449" s="7">
         <v>320</v>
@@ -15133,10 +15152,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
@@ -15154,7 +15173,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F450" s="7">
         <v>320</v>
@@ -15163,13 +15182,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H450" s="8">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -15187,22 +15206,22 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F451" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G451" s="8">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="H451" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -15235,22 +15254,22 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F453" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G453" s="8">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c t="s" r="H453" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I453" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
@@ -15268,7 +15287,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
@@ -15280,10 +15299,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -15316,7 +15335,7 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F456" s="7">
         <v>330</v>
@@ -15325,20 +15344,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H456" s="8">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c t="s" r="I456" s="7">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="K456" s="7">
         <v>78</v>
       </c>
       <c r="L456" s="7"/>
       <c t="s" r="M456" s="7">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="457" ht="14.25" customHeight="1">
@@ -15353,13 +15372,13 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F457" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G457" s="8">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c t="s" r="H457" s="8">
         <v>16</v>
@@ -15371,11 +15390,11 @@
         <v>18</v>
       </c>
       <c t="s" r="K457" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L457" s="7"/>
       <c t="s" r="M457" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="458" ht="14.25" customHeight="1">
@@ -15405,7 +15424,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F459" s="7">
         <v>330</v>
@@ -15417,10 +15436,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
@@ -15438,7 +15457,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F460" s="7">
         <v>330</v>
@@ -15447,10 +15466,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H460" s="8">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c t="s" r="I460" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J460" s="7">
         <v>160</v>
@@ -15471,19 +15490,19 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F461" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G461" s="8">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c t="s" r="H461" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J461" s="7">
         <v>156</v>
@@ -15519,7 +15538,7 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F463" s="7">
         <v>330</v>
@@ -15528,13 +15547,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H463" s="8">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
@@ -15552,22 +15571,22 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F464" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G464" s="8">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c t="s" r="H464" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
@@ -15596,11 +15615,11 @@
         <v>5805</v>
       </c>
       <c t="s" r="C466" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F466" s="7">
         <v>330</v>
@@ -15609,13 +15628,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H466" s="8">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c t="s" r="I466" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J466" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K466" s="7"/>
       <c r="L466" s="7"/>
@@ -15629,23 +15648,23 @@
         <v>5806</v>
       </c>
       <c t="s" r="C467" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F467" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G467" s="8">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c t="s" r="H467" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I467" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J467" s="7">
         <v>133</v>
@@ -15681,7 +15700,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F469" s="7">
         <v>330</v>
@@ -15690,10 +15709,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H469" s="8">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J469" s="7">
         <v>109</v>
@@ -15714,22 +15733,22 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F470" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G470" s="8">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c t="s" r="H470" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
@@ -15737,7 +15756,7 @@
     </row>
     <row r="471" ht="15.75" customHeight="1">
       <c t="s" r="A471" s="9">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B471" s="9"/>
       <c r="C471" s="9"/>
@@ -15757,7 +15776,7 @@
     <row r="472" ht="65.25" customHeight="1"/>
     <row r="473" ht="16.5" customHeight="1">
       <c t="s" r="A473" s="10">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B473" s="10"/>
       <c r="C473" s="10"/>
@@ -15770,7 +15789,7 @@
       <c r="J473" s="10"/>
       <c r="K473" s="10"/>
       <c t="s" r="L473" s="11">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="M473" s="11"/>
       <c r="N473" s="11"/>

--- a/Data/FlightPlan/FPL_21AUG26.xlsx
+++ b/Data/FlightPlan/FPL_21AUG26.xlsx
@@ -512,6 +512,9 @@
     <t>09:55</t>
   </si>
   <si>
+    <t>09:53</t>
+  </si>
+  <si>
     <t>BMV</t>
   </si>
   <si>
@@ -584,7 +587,7 @@
     <t>09:40</t>
   </si>
   <si>
-    <t>10:07</t>
+    <t>09:39</t>
   </si>
   <si>
     <t>13:10</t>
@@ -647,12 +650,18 @@
     <t>VN-A550</t>
   </si>
   <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
     <t>08:45</t>
   </si>
   <si>
-    <t>11:25</t>
-  </si>
-  <si>
     <t>14:05</t>
   </si>
   <si>
@@ -668,12 +677,6 @@
     <t>18:55</t>
   </si>
   <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
     <t>01:00</t>
   </si>
   <si>
@@ -983,6 +986,9 @@
     <t>VN-A650</t>
   </si>
   <si>
+    <t>06:48</t>
+  </si>
+  <si>
     <t>VCL</t>
   </si>
   <si>
@@ -998,6 +1004,9 @@
     <t>07:40</t>
   </si>
   <si>
+    <t>07:28</t>
+  </si>
+  <si>
     <t>PER</t>
   </si>
   <si>
@@ -1055,7 +1064,7 @@
     <t>VN-A667</t>
   </si>
   <si>
-    <t>06:33</t>
+    <t>06:46</t>
   </si>
   <si>
     <t>07:20</t>
@@ -1115,6 +1124,9 @@
     <t>VN-A683</t>
   </si>
   <si>
+    <t>06:43</t>
+  </si>
+  <si>
     <t>10:25</t>
   </si>
   <si>
@@ -1163,9 +1175,6 @@
     <t>VN-A698</t>
   </si>
   <si>
-    <t>06:57</t>
-  </si>
-  <si>
     <t>VN-A699</t>
   </si>
   <si>
@@ -1229,7 +1238,7 @@
     <t>Total Record(s): 388</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 21, 2026 05:09</t>
+    <t xml:space="preserve">Generated on  Aug 21, 2026 05:50</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4151,7 +4160,9 @@
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
-      <c r="M85" s="7"/>
+      <c t="s" r="M85" s="7">
+        <v>156</v>
+      </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c t="s" r="A86" s="6">
@@ -4430,7 +4441,9 @@
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
-      <c r="M94" s="7"/>
+      <c t="s" r="M94" s="7">
+        <v>167</v>
+      </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c t="s" r="A95" s="6">
@@ -4453,13 +4466,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4483,7 +4496,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="H96" s="8">
         <v>39</v>
@@ -4525,7 +4538,7 @@
         <v>161</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4585,13 +4598,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4615,16 +4628,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H100" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4657,7 +4670,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4666,10 +4679,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>20</v>
@@ -4690,13 +4703,13 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>16</v>
@@ -4705,7 +4718,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4723,7 +4736,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4756,7 +4769,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4768,10 +4781,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4804,7 +4817,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4837,7 +4850,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4870,7 +4883,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4882,10 +4895,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4903,7 +4916,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -4936,7 +4949,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4969,7 +4982,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -4981,10 +4994,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -5002,7 +5015,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5017,7 +5030,7 @@
         <v>140</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5035,7 +5048,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5047,10 +5060,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5083,7 +5096,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5098,12 +5111,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5118,7 +5131,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5130,10 +5143,10 @@
         <v>148</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5151,7 +5164,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5163,7 +5176,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>58</v>
@@ -5199,7 +5212,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5232,7 +5245,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5244,7 +5257,7 @@
         <v>87</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J121" s="7">
         <v>85</v>
@@ -5265,7 +5278,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5277,7 +5290,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>23</v>
@@ -5298,7 +5311,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5310,7 +5323,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J123" s="7">
         <v>44</v>
@@ -5331,7 +5344,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5346,7 +5359,7 @@
         <v>150</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5364,7 +5377,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5379,7 +5392,7 @@
         <v>163</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5412,7 +5425,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5427,7 +5440,7 @@
         <v>20</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5445,7 +5458,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5478,7 +5491,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5493,7 +5506,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5511,7 +5524,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5544,7 +5557,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5556,7 +5569,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J131" s="7">
         <v>75</v>
@@ -5577,7 +5590,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5589,10 +5602,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5625,7 +5638,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5640,7 +5653,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5658,7 +5671,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5691,7 +5704,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5703,7 +5716,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>52</v>
@@ -5739,7 +5752,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5748,7 +5761,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="I138" s="7">
         <v>147</v>
@@ -5772,13 +5785,13 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>16</v>
@@ -5787,7 +5800,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5805,7 +5818,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5838,7 +5851,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5850,10 +5863,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5871,7 +5884,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5886,7 +5899,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5912,14 +5925,14 @@
         <v>13</v>
       </c>
       <c r="B144" s="7">
-        <v>447</v>
+        <v>133</v>
       </c>
       <c t="s" r="C144" s="7">
         <v>14</v>
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5928,13 +5941,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5945,29 +5958,29 @@
         <v>13</v>
       </c>
       <c r="B145" s="7">
-        <v>440</v>
+        <v>140</v>
       </c>
       <c t="s" r="C145" s="7">
         <v>14</v>
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c t="s" r="H145" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5978,14 +5991,14 @@
         <v>13</v>
       </c>
       <c r="B146" s="7">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c t="s" r="C146" s="7">
         <v>14</v>
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -5997,10 +6010,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>215</v>
+        <v>58</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6011,14 +6024,14 @@
         <v>13</v>
       </c>
       <c r="B147" s="7">
-        <v>331</v>
+        <v>160</v>
       </c>
       <c t="s" r="C147" s="7">
         <v>14</v>
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6027,47 +6040,29 @@
         <v>16</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c r="M147" s="7"/>
     </row>
     <row r="148" ht="14.25" customHeight="1">
-      <c t="s" r="A148" s="6">
-        <v>13</v>
-      </c>
-      <c r="B148" s="7">
-        <v>328</v>
-      </c>
-      <c t="s" r="C148" s="7">
-        <v>14</v>
-      </c>
+      <c r="A148" s="6"/>
+      <c r="B148" s="7"/>
+      <c r="C148" s="7"/>
       <c r="D148" s="7"/>
-      <c t="s" r="E148" s="7">
-        <v>211</v>
-      </c>
-      <c r="F148" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G148" s="8">
-        <v>79</v>
-      </c>
-      <c t="s" r="H148" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I148" s="7">
-        <v>218</v>
-      </c>
-      <c t="s" r="J148" s="7">
-        <v>163</v>
-      </c>
+      <c r="E148" s="7"/>
+      <c r="F148" s="7"/>
+      <c r="G148" s="8"/>
+      <c r="H148" s="8"/>
+      <c r="I148" s="7"/>
+      <c r="J148" s="7"/>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c r="M148" s="7"/>
@@ -6077,45 +6072,63 @@
         <v>13</v>
       </c>
       <c r="B149" s="7">
-        <v>160</v>
+        <v>447</v>
       </c>
       <c t="s" r="C149" s="7">
         <v>14</v>
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>188</v>
+        <v>137</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c r="M149" s="7"/>
     </row>
     <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="6"/>
-      <c r="B150" s="7"/>
-      <c r="C150" s="7"/>
+      <c t="s" r="A150" s="6">
+        <v>13</v>
+      </c>
+      <c r="B150" s="7">
+        <v>440</v>
+      </c>
+      <c t="s" r="C150" s="7">
+        <v>14</v>
+      </c>
       <c r="D150" s="7"/>
-      <c r="E150" s="7"/>
-      <c r="F150" s="7"/>
-      <c r="G150" s="8"/>
-      <c r="H150" s="8"/>
-      <c r="I150" s="7"/>
-      <c r="J150" s="7"/>
+      <c t="s" r="E150" s="7">
+        <v>215</v>
+      </c>
+      <c r="F150" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G150" s="8">
+        <v>79</v>
+      </c>
+      <c t="s" r="H150" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I150" s="7">
+        <v>213</v>
+      </c>
+      <c t="s" r="J150" s="7">
+        <v>56</v>
+      </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c r="M150" s="7"/>
@@ -6125,14 +6138,14 @@
         <v>13</v>
       </c>
       <c r="B151" s="7">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c t="s" r="C151" s="7">
         <v>14</v>
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6144,10 +6157,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>56</v>
+        <v>218</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6158,29 +6171,29 @@
         <v>13</v>
       </c>
       <c r="B152" s="7">
-        <v>140</v>
+        <v>331</v>
       </c>
       <c t="s" r="C152" s="7">
         <v>14</v>
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
+        <v>215</v>
+      </c>
+      <c r="F152" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G152" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H152" s="8">
+        <v>79</v>
+      </c>
+      <c t="s" r="I152" s="7">
+        <v>219</v>
+      </c>
+      <c t="s" r="J152" s="7">
         <v>220</v>
-      </c>
-      <c r="F152" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G152" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H152" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I152" s="7">
-        <v>196</v>
-      </c>
-      <c t="s" r="J152" s="7">
-        <v>129</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6191,29 +6204,29 @@
         <v>13</v>
       </c>
       <c r="B153" s="7">
-        <v>151</v>
+        <v>328</v>
       </c>
       <c t="s" r="C153" s="7">
         <v>14</v>
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>58</v>
+        <v>163</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6231,7 +6244,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6243,7 +6256,7 @@
         <v>77</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>146</v>
@@ -6279,7 +6292,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6291,10 +6304,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6312,7 +6325,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6327,7 +6340,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6345,7 +6358,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6357,7 +6370,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J158" s="7">
         <v>59</v>
@@ -6378,7 +6391,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6390,10 +6403,10 @@
         <v>61</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6426,22 +6439,22 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6461,7 +6474,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6494,7 +6507,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6506,7 +6519,7 @@
         <v>87</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>80</v>
@@ -6527,7 +6540,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6539,10 +6552,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6560,7 +6573,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6575,7 +6588,7 @@
         <v>119</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6593,7 +6606,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6626,7 +6639,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6638,10 +6651,10 @@
         <v>61</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6674,7 +6687,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6689,7 +6702,7 @@
         <v>99</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6707,7 +6720,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6719,7 +6732,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J170" s="7">
         <v>86</v>
@@ -6740,7 +6753,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6773,7 +6786,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6785,7 +6798,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>57</v>
@@ -6806,7 +6819,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6815,13 +6828,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="I173" s="7">
         <v>163</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6839,22 +6852,22 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6887,7 +6900,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6920,11 +6933,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C177" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6957,11 +6970,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C178" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6970,20 +6983,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="K178" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -6994,26 +7007,26 @@
         <v>5069</v>
       </c>
       <c t="s" r="C179" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7046,7 +7059,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7055,10 +7068,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>63</v>
@@ -7079,13 +7092,13 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>16</v>
@@ -7094,7 +7107,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7112,7 +7125,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7121,13 +7134,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7145,13 +7158,13 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>16</v>
@@ -7160,7 +7173,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7189,26 +7202,26 @@
         <v>7615</v>
       </c>
       <c t="s" r="C186" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7222,11 +7235,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C187" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7255,11 +7268,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C188" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7271,10 +7284,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7288,11 +7301,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C189" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7301,10 +7314,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>49</v>
@@ -7340,7 +7353,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7355,7 +7368,7 @@
         <v>156</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7373,7 +7386,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7385,7 +7398,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J192" s="7">
         <v>80</v>
@@ -7406,7 +7419,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7415,13 +7428,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="I193" s="7">
         <v>150</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7439,22 +7452,22 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7487,7 +7500,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7502,7 +7515,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7520,7 +7533,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7535,7 +7548,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7553,7 +7566,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7568,7 +7581,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7601,7 +7614,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7610,7 +7623,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="I200" s="7">
         <v>154</v>
@@ -7634,13 +7647,13 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="H201" s="8">
         <v>16</v>
@@ -7649,7 +7662,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7667,7 +7680,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7682,7 +7695,7 @@
         <v>136</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7700,7 +7713,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7712,7 +7725,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>57</v>
@@ -7733,7 +7746,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7742,13 +7755,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7766,22 +7779,22 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7814,7 +7827,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7823,13 +7836,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="I207" s="7">
         <v>133</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7847,19 +7860,19 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>72</v>
@@ -7880,7 +7893,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7892,7 +7905,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>158</v>
@@ -7913,7 +7926,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7928,7 +7941,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7946,7 +7959,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7961,7 +7974,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7979,7 +7992,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7991,10 +8004,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8027,7 +8040,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8039,7 +8052,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>147</v>
@@ -8047,7 +8060,7 @@
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8062,7 +8075,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8095,7 +8108,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8104,13 +8117,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="I216" s="7">
         <v>108</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8128,22 +8141,22 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8161,7 +8174,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8170,10 +8183,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J218" s="7">
         <v>111</v>
@@ -8209,7 +8222,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8224,7 +8237,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8242,7 +8255,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8257,7 +8270,7 @@
         <v>157</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8275,7 +8288,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8287,10 +8300,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8323,7 +8336,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8335,10 +8348,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8356,7 +8369,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8365,13 +8378,13 @@
         <v>39</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I225" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8389,13 +8402,13 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>39</v>
@@ -8404,7 +8417,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8422,7 +8435,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8470,7 +8483,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8485,7 +8498,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8503,7 +8516,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8515,10 +8528,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8536,7 +8549,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8551,7 +8564,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8569,7 +8582,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8584,7 +8597,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8602,7 +8615,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8635,7 +8648,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8647,7 +8660,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>90</v>
@@ -8668,7 +8681,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8701,7 +8714,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8713,10 +8726,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8749,7 +8762,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8761,10 +8774,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8782,7 +8795,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8797,7 +8810,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8815,7 +8828,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8848,7 +8861,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8860,10 +8873,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8881,7 +8894,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8914,7 +8927,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8926,10 +8939,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8962,7 +8975,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -8974,7 +8987,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J245" s="7">
         <v>137</v>
@@ -8995,7 +9008,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9007,10 +9020,10 @@
         <v>98</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9028,7 +9041,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9043,7 +9056,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9061,7 +9074,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9070,13 +9083,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9094,22 +9107,22 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9127,7 +9140,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9142,7 +9155,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9160,7 +9173,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9175,7 +9188,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9208,7 +9221,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9223,7 +9236,7 @@
         <v>156</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9241,7 +9254,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9253,7 +9266,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J254" s="7">
         <v>127</v>
@@ -9274,7 +9287,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9307,7 +9320,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9319,10 +9332,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9340,7 +9353,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9355,7 +9368,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9373,7 +9386,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9385,10 +9398,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9421,7 +9434,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9433,7 +9446,7 @@
         <v>87</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>97</v>
@@ -9454,7 +9467,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9469,7 +9482,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9487,7 +9500,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9502,7 +9515,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9520,7 +9533,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9532,7 +9545,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>82</v>
@@ -9568,7 +9581,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9580,10 +9593,10 @@
         <v>104</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9601,7 +9614,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9616,7 +9629,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9634,7 +9647,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9649,7 +9662,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9667,7 +9680,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9682,7 +9695,7 @@
         <v>119</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9700,7 +9713,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9715,7 +9728,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9733,7 +9746,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9766,7 +9779,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9778,7 +9791,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>124</v>
@@ -9814,7 +9827,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9847,7 +9860,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9880,7 +9893,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9892,10 +9905,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9913,7 +9926,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -9925,10 +9938,10 @@
         <v>98</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9946,7 +9959,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -9994,7 +10007,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10006,7 +10019,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>20</v>
@@ -10027,7 +10040,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10060,7 +10073,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10072,10 +10085,10 @@
         <v>79</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10093,7 +10106,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10108,7 +10121,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10126,7 +10139,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10138,7 +10151,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>121</v>
@@ -10159,7 +10172,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10174,7 +10187,7 @@
         <v>141</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10207,7 +10220,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10222,7 +10235,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10240,7 +10253,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10252,7 +10265,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>106</v>
@@ -10273,7 +10286,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10285,7 +10298,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>88</v>
@@ -10306,7 +10319,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10315,10 +10328,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>83</v>
@@ -10339,22 +10352,22 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10387,7 +10400,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -10399,14 +10412,16 @@
         <v>115</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
-      <c r="M292" s="7"/>
+      <c t="s" r="M292" s="7">
+        <v>325</v>
+      </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
       <c t="s" r="A293" s="6">
@@ -10420,7 +10435,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10435,7 +10450,7 @@
         <v>165</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10453,7 +10468,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10462,13 +10477,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="I294" s="7">
         <v>126</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10486,13 +10501,13 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>16</v>
@@ -10519,7 +10534,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10531,10 +10546,10 @@
         <v>128</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10552,7 +10567,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10567,7 +10582,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10585,7 +10600,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10594,13 +10609,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10618,13 +10633,13 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>16</v>
@@ -10633,7 +10648,7 @@
         <v>140</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10666,7 +10681,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10681,11 +10696,13 @@
         <v>69</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
-      <c r="M301" s="7"/>
+      <c t="s" r="M301" s="7">
+        <v>331</v>
+      </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
       <c t="s" r="A302" s="6">
@@ -10699,7 +10716,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -10732,7 +10749,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -10765,7 +10782,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -10777,7 +10794,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>24</v>
@@ -10798,7 +10815,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -10810,10 +10827,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10831,7 +10848,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -10840,10 +10857,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>97</v>
@@ -10879,7 +10896,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -10888,7 +10905,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="I308" s="7">
         <v>42</v>
@@ -10912,13 +10929,13 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>16</v>
@@ -10927,7 +10944,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10945,7 +10962,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -10957,7 +10974,7 @@
         <v>115</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>82</v>
@@ -10978,7 +10995,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -10990,10 +11007,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11026,7 +11043,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11059,7 +11076,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11071,10 +11088,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11092,7 +11109,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11107,7 +11124,7 @@
         <v>127</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11125,7 +11142,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11134,10 +11151,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>88</v>
@@ -11158,19 +11175,19 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>67</v>
@@ -11206,7 +11223,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11218,10 +11235,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11239,7 +11256,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11287,7 +11304,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11296,13 +11313,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11320,13 +11337,13 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>17</v>
@@ -11353,7 +11370,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11362,13 +11379,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11386,22 +11403,22 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11419,7 +11436,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11428,13 +11445,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c t="s" r="I326" s="7">
         <v>129</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11452,22 +11469,22 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c t="s" r="H327" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11500,7 +11517,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11509,13 +11526,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="I329" s="7">
         <v>124</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11533,19 +11550,19 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="H330" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>137</v>
@@ -11566,7 +11583,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11578,7 +11595,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>159</v>
@@ -11599,7 +11616,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11614,7 +11631,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11632,7 +11649,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11644,10 +11661,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11665,7 +11682,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11680,7 +11697,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11713,7 +11730,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -11746,7 +11763,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11758,10 +11775,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11779,7 +11796,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -11794,7 +11811,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11812,7 +11829,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -11824,10 +11841,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11845,7 +11862,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -11854,10 +11871,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>34</v>
@@ -11878,22 +11895,22 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11926,7 +11943,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -11938,15 +11955,15 @@
         <v>51</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -11961,7 +11978,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -11970,13 +11987,13 @@
         <v>51</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11994,22 +12011,22 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>51</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12027,7 +12044,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12060,7 +12077,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12069,13 +12086,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12093,13 +12110,13 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>16</v>
@@ -12141,7 +12158,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12156,7 +12173,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12174,7 +12191,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12189,7 +12206,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12207,7 +12224,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12219,7 +12236,7 @@
         <v>115</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>26</v>
@@ -12240,7 +12257,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12288,7 +12305,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12300,10 +12317,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12321,7 +12338,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12333,7 +12350,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>56</v>
@@ -12354,7 +12371,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12366,10 +12383,10 @@
         <v>87</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12387,7 +12404,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -12420,7 +12437,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
@@ -12429,13 +12446,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12453,22 +12470,22 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12501,13 +12518,13 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>17</v>
@@ -12534,7 +12551,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12567,7 +12584,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12579,7 +12596,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="J364" s="7">
         <v>117</v>
@@ -12600,7 +12617,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12633,7 +12650,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12645,10 +12662,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12666,7 +12683,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12678,7 +12695,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>153</v>
@@ -12714,7 +12731,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -12729,7 +12746,7 @@
         <v>154</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12747,7 +12764,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -12780,7 +12797,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -12792,7 +12809,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>63</v>
@@ -12813,7 +12830,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -12825,7 +12842,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="J372" s="7">
         <v>44</v>
@@ -12846,7 +12863,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -12861,7 +12878,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12879,7 +12896,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -12891,10 +12908,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I374" s="7">
+        <v>363</v>
+      </c>
+      <c t="s" r="J374" s="7">
         <v>360</v>
-      </c>
-      <c t="s" r="J374" s="7">
-        <v>357</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12912,7 +12929,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -12924,10 +12941,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12960,7 +12977,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -12972,10 +12989,10 @@
         <v>22</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12993,7 +13010,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -13005,7 +13022,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>78</v>
@@ -13026,7 +13043,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -13074,7 +13091,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13086,7 +13103,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>136</v>
@@ -13107,7 +13124,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13116,10 +13133,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="J382" s="7">
         <v>80</v>
@@ -13140,13 +13157,13 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>27</v>
@@ -13155,7 +13172,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13173,7 +13190,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13182,13 +13199,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13206,22 +13223,22 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13254,7 +13271,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13287,7 +13304,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
@@ -13296,7 +13313,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c t="s" r="I388" s="7">
         <v>65</v>
@@ -13320,13 +13337,13 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c t="s" r="H389" s="8">
         <v>16</v>
@@ -13335,7 +13352,7 @@
         <v>163</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13368,7 +13385,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -13383,7 +13400,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13401,7 +13418,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -13413,7 +13430,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J392" s="7">
         <v>49</v>
@@ -13434,7 +13451,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -13467,7 +13484,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -13500,7 +13517,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -13512,10 +13529,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13533,7 +13550,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -13545,10 +13562,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13566,7 +13583,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -13578,10 +13595,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13599,7 +13616,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -13647,7 +13664,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -13666,7 +13683,9 @@
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
-      <c r="M400" s="7"/>
+      <c t="s" r="M400" s="7">
+        <v>371</v>
+      </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
       <c t="s" r="A401" s="6">
@@ -13680,7 +13699,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -13713,7 +13732,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -13725,7 +13744,7 @@
         <v>104</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>56</v>
@@ -13746,7 +13765,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -13758,10 +13777,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13779,7 +13798,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -13788,13 +13807,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13812,13 +13831,13 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c t="s" r="H405" s="8">
         <v>16</v>
@@ -13827,7 +13846,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13860,7 +13879,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -13872,10 +13891,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13893,7 +13912,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -13905,7 +13924,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>53</v>
@@ -13926,7 +13945,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -13938,7 +13957,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J409" s="7">
         <v>127</v>
@@ -13959,7 +13978,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -13974,7 +13993,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -13992,7 +14011,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14007,7 +14026,7 @@
         <v>161</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14025,7 +14044,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14037,10 +14056,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14058,7 +14077,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -14070,10 +14089,10 @@
         <v>61</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14106,7 +14125,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -14118,10 +14137,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14139,7 +14158,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14151,10 +14170,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14172,7 +14191,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14184,10 +14203,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14205,7 +14224,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14217,10 +14236,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14253,7 +14272,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -14262,7 +14281,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c t="s" r="I420" s="7">
         <v>20</v>
@@ -14286,13 +14305,13 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G421" s="8">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c t="s" r="H421" s="8">
         <v>16</v>
@@ -14319,7 +14338,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -14328,10 +14347,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>66</v>
@@ -14352,22 +14371,22 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14385,7 +14404,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -14397,7 +14416,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>31</v>
@@ -14418,7 +14437,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -14430,10 +14449,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14466,7 +14485,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
@@ -14499,7 +14518,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
@@ -14532,7 +14551,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F429" s="7">
         <v>320</v>
@@ -14547,7 +14566,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -14565,7 +14584,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F430" s="7">
         <v>320</v>
@@ -14580,7 +14599,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14598,7 +14617,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F431" s="7">
         <v>320</v>
@@ -14607,13 +14626,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H431" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14631,19 +14650,19 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F432" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G432" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="H432" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c t="s" r="J432" s="7">
         <v>109</v>
@@ -14679,7 +14698,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -14688,10 +14707,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J434" s="7">
         <v>78</v>
@@ -14712,13 +14731,13 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="H435" s="8">
         <v>17</v>
@@ -14727,7 +14746,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -14745,7 +14764,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
@@ -14757,10 +14776,10 @@
         <v>77</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -14793,7 +14812,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
@@ -14805,7 +14824,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c t="s" r="J438" s="7">
         <v>124</v>
@@ -14813,7 +14832,7 @@
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
       <c t="s" r="M438" s="7">
-        <v>384</v>
+        <v>376</v>
       </c>
     </row>
     <row r="439" ht="14.25" customHeight="1">
@@ -14828,7 +14847,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -14840,7 +14859,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="J439" s="7">
         <v>53</v>
@@ -14861,7 +14880,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
@@ -14894,7 +14913,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -14906,7 +14925,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J441" s="7">
         <v>160</v>
@@ -14927,7 +14946,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F442" s="7">
         <v>321</v>
@@ -14936,13 +14955,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H442" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="I442" s="7">
         <v>129</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -14960,13 +14979,13 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="H443" s="8">
         <v>16</v>
@@ -14975,7 +14994,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -15008,7 +15027,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F445" s="7">
         <v>320</v>
@@ -15020,7 +15039,7 @@
         <v>115</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c t="s" r="J445" s="7">
         <v>147</v>
@@ -15041,7 +15060,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F446" s="7">
         <v>320</v>
@@ -15053,7 +15072,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J446" s="7">
         <v>85</v>
@@ -15074,7 +15093,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F447" s="7">
         <v>320</v>
@@ -15083,13 +15102,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H447" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -15107,13 +15126,13 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F448" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G448" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="H448" s="8">
         <v>16</v>
@@ -15122,7 +15141,7 @@
         <v>149</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -15140,7 +15159,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F449" s="7">
         <v>320</v>
@@ -15152,10 +15171,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
@@ -15173,7 +15192,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F450" s="7">
         <v>320</v>
@@ -15182,13 +15201,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H450" s="8">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -15206,22 +15225,22 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F451" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G451" s="8">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c t="s" r="H451" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -15254,22 +15273,22 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F453" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G453" s="8">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c t="s" r="H453" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I453" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
@@ -15287,7 +15306,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
@@ -15299,10 +15318,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -15335,7 +15354,7 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F456" s="7">
         <v>330</v>
@@ -15344,20 +15363,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H456" s="8">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c t="s" r="I456" s="7">
         <v>85</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="K456" s="7">
         <v>78</v>
       </c>
       <c r="L456" s="7"/>
       <c t="s" r="M456" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="457" ht="14.25" customHeight="1">
@@ -15372,29 +15391,29 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F457" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G457" s="8">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c t="s" r="H457" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I457" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J457" s="7">
         <v>18</v>
       </c>
       <c t="s" r="K457" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L457" s="7"/>
       <c t="s" r="M457" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="458" ht="14.25" customHeight="1">
@@ -15424,7 +15443,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F459" s="7">
         <v>330</v>
@@ -15436,10 +15455,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
@@ -15457,7 +15476,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F460" s="7">
         <v>330</v>
@@ -15466,10 +15485,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H460" s="8">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c t="s" r="I460" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J460" s="7">
         <v>160</v>
@@ -15490,19 +15509,19 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F461" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G461" s="8">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c t="s" r="H461" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c t="s" r="J461" s="7">
         <v>156</v>
@@ -15538,7 +15557,7 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F463" s="7">
         <v>330</v>
@@ -15547,13 +15566,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H463" s="8">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
@@ -15571,22 +15590,22 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F464" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G464" s="8">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c t="s" r="H464" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
@@ -15615,11 +15634,11 @@
         <v>5805</v>
       </c>
       <c t="s" r="C466" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F466" s="7">
         <v>330</v>
@@ -15628,13 +15647,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H466" s="8">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c t="s" r="I466" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J466" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K466" s="7"/>
       <c r="L466" s="7"/>
@@ -15648,23 +15667,23 @@
         <v>5806</v>
       </c>
       <c t="s" r="C467" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F467" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G467" s="8">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c t="s" r="H467" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I467" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J467" s="7">
         <v>133</v>
@@ -15700,7 +15719,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F469" s="7">
         <v>330</v>
@@ -15709,10 +15728,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H469" s="8">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J469" s="7">
         <v>109</v>
@@ -15733,22 +15752,22 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F470" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G470" s="8">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c t="s" r="H470" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
@@ -15756,7 +15775,7 @@
     </row>
     <row r="471" ht="15.75" customHeight="1">
       <c t="s" r="A471" s="9">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B471" s="9"/>
       <c r="C471" s="9"/>
@@ -15776,7 +15795,7 @@
     <row r="472" ht="65.25" customHeight="1"/>
     <row r="473" ht="16.5" customHeight="1">
       <c t="s" r="A473" s="10">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B473" s="10"/>
       <c r="C473" s="10"/>
@@ -15789,7 +15808,7 @@
       <c r="J473" s="10"/>
       <c r="K473" s="10"/>
       <c t="s" r="L473" s="11">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="M473" s="11"/>
       <c r="N473" s="11"/>
